--- a/Auction Database 2026.xlsx
+++ b/Auction Database 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="181">
   <si>
     <t>Item Name</t>
   </si>
@@ -561,6 +561,15 @@
   </si>
   <si>
     <t>Fred Wang</t>
+  </si>
+  <si>
+    <t>Gas Furnace Replacement Sizing Consultation</t>
+  </si>
+  <si>
+    <t>Norman Bair will provide a consultation on the size of furnace needed for your space so you know what size furnace the contractor should be installing to prevent oversizing.</t>
+  </si>
+  <si>
+    <t>Norman Bair</t>
   </si>
 </sst>
 </file>
@@ -1099,17 +1108,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1136,10 +1145,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1378,12 +1387,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1660,7 +1669,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1687,10 +1696,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -4865,7 +4874,7 @@
         <v>100</v>
       </c>
       <c r="G64" s="21">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H64" s="21">
         <v>10</v>
@@ -4892,15 +4901,31 @@
       <c r="Z64" s="12"/>
     </row>
     <row r="65" ht="13.65" customHeight="1">
-      <c r="A65" s="16"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
+      <c r="A65" t="s" s="14">
+        <v>178</v>
+      </c>
+      <c r="B65" s="34">
+        <v>64</v>
+      </c>
+      <c r="C65" t="s" s="14">
+        <v>179</v>
+      </c>
       <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="16"/>
+      <c r="E65" t="s" s="14">
+        <v>180</v>
+      </c>
+      <c r="F65" s="35">
+        <v>30</v>
+      </c>
+      <c r="G65" s="21">
+        <v>10</v>
+      </c>
+      <c r="H65" s="21">
+        <v>5</v>
+      </c>
+      <c r="I65" t="s" s="14">
+        <v>25</v>
+      </c>
       <c r="J65" s="16"/>
       <c r="K65" s="12"/>
       <c r="L65" s="12"/>
@@ -5005,7 +5030,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C64" r:id="rId1" location="" tooltip="" display="Sugar &amp; Sage (@sugarnsagewi)&#10;"/>
+    <hyperlink ref="C64" r:id="rId1" location="" tooltip="" display="$50 Fresh baked sweet plus $50 gift. Local bakery. Instagram Sugar &amp; Sage (@sugarnsagewi)&#10;"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="65" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>

--- a/Auction Database 2026.xlsx
+++ b/Auction Database 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="193">
   <si>
     <t>Item Name</t>
   </si>
@@ -570,6 +570,42 @@
   </si>
   <si>
     <t>Norman Bair</t>
+  </si>
+  <si>
+    <t>Full-Size Handmade Quilt</t>
+  </si>
+  <si>
+    <t>Beautiful handmade sampler quilt. Size is 60" x 80" to fit a full-size bed.</t>
+  </si>
+  <si>
+    <t>Helen Martin</t>
+  </si>
+  <si>
+    <t>$25 to Banzo Restaurant</t>
+  </si>
+  <si>
+    <t>$25 gift card to Banzo restaurant on Sherman Ave. specializing in falafel &amp; other Mediterranean fare.</t>
+  </si>
+  <si>
+    <t>Banzo</t>
+  </si>
+  <si>
+    <t>$20 to Johnson Public House and a Bag of Coffee</t>
+  </si>
+  <si>
+    <t>$20 gift card to Johnson Public House coffee shop on Johnson St and a bag of coffee.</t>
+  </si>
+  <si>
+    <t>Johnson Public House</t>
+  </si>
+  <si>
+    <t>Door County Basket</t>
+  </si>
+  <si>
+    <t>A package filled with the flavors of Door County.</t>
+  </si>
+  <si>
+    <t>Jerry VanKirk</t>
   </si>
 </sst>
 </file>
@@ -1941,7 +1977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Z77"/>
   <sheetFormatPr defaultColWidth="14.5" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="24.3516" style="1" customWidth="1"/>
@@ -4945,14 +4981,28 @@
       <c r="Z65" s="12"/>
     </row>
     <row r="66" ht="13.65" customHeight="1">
-      <c r="A66" s="16"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
+      <c r="A66" t="s" s="14">
+        <v>181</v>
+      </c>
+      <c r="B66" s="34">
+        <v>65</v>
+      </c>
+      <c r="C66" t="s" s="14">
+        <v>182</v>
+      </c>
       <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
+      <c r="E66" t="s" s="14">
+        <v>183</v>
+      </c>
+      <c r="F66" s="35">
+        <v>350</v>
+      </c>
+      <c r="G66" s="21">
+        <v>150</v>
+      </c>
+      <c r="H66" s="21">
+        <v>20</v>
+      </c>
       <c r="I66" s="16"/>
       <c r="J66" s="16"/>
       <c r="K66" s="12"/>
@@ -4973,14 +5023,28 @@
       <c r="Z66" s="12"/>
     </row>
     <row r="67" ht="13.65" customHeight="1">
-      <c r="A67" s="16"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
+      <c r="A67" t="s" s="14">
+        <v>184</v>
+      </c>
+      <c r="B67" s="34">
+        <v>66</v>
+      </c>
+      <c r="C67" t="s" s="14">
+        <v>185</v>
+      </c>
       <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
+      <c r="E67" t="s" s="14">
+        <v>186</v>
+      </c>
+      <c r="F67" s="35">
+        <v>25</v>
+      </c>
+      <c r="G67" s="21">
+        <v>10</v>
+      </c>
+      <c r="H67" s="21">
+        <v>2</v>
+      </c>
       <c r="I67" s="16"/>
       <c r="J67" s="16"/>
       <c r="K67" s="12"/>
@@ -5001,14 +5065,28 @@
       <c r="Z67" s="12"/>
     </row>
     <row r="68" ht="13.65" customHeight="1">
-      <c r="A68" s="16"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
+      <c r="A68" t="s" s="14">
+        <v>184</v>
+      </c>
+      <c r="B68" s="34">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s" s="14">
+        <v>185</v>
+      </c>
       <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
+      <c r="E68" t="s" s="14">
+        <v>186</v>
+      </c>
+      <c r="F68" s="35">
+        <v>25</v>
+      </c>
+      <c r="G68" s="21">
+        <v>10</v>
+      </c>
+      <c r="H68" s="21">
+        <v>2</v>
+      </c>
       <c r="I68" s="16"/>
       <c r="J68" s="16"/>
       <c r="K68" s="12"/>
@@ -5028,6 +5106,300 @@
       <c r="Y68" s="12"/>
       <c r="Z68" s="12"/>
     </row>
+    <row r="69" ht="13.65" customHeight="1">
+      <c r="A69" t="s" s="14">
+        <v>187</v>
+      </c>
+      <c r="B69" s="34">
+        <v>68</v>
+      </c>
+      <c r="C69" t="s" s="14">
+        <v>188</v>
+      </c>
+      <c r="D69" s="16"/>
+      <c r="E69" t="s" s="14">
+        <v>189</v>
+      </c>
+      <c r="F69" s="35">
+        <v>32</v>
+      </c>
+      <c r="G69" s="21">
+        <v>15</v>
+      </c>
+      <c r="H69" s="21">
+        <v>5</v>
+      </c>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="12"/>
+      <c r="O69" s="12"/>
+      <c r="P69" s="12"/>
+      <c r="Q69" s="12"/>
+      <c r="R69" s="12"/>
+      <c r="S69" s="12"/>
+      <c r="T69" s="12"/>
+      <c r="U69" s="12"/>
+      <c r="V69" s="12"/>
+      <c r="W69" s="12"/>
+      <c r="X69" s="12"/>
+      <c r="Y69" s="12"/>
+      <c r="Z69" s="12"/>
+    </row>
+    <row r="70" ht="13.65" customHeight="1">
+      <c r="A70" t="s" s="14">
+        <v>187</v>
+      </c>
+      <c r="B70" s="34">
+        <v>69</v>
+      </c>
+      <c r="C70" t="s" s="14">
+        <v>188</v>
+      </c>
+      <c r="D70" s="16"/>
+      <c r="E70" t="s" s="14">
+        <v>189</v>
+      </c>
+      <c r="F70" s="35">
+        <v>32</v>
+      </c>
+      <c r="G70" s="21">
+        <v>15</v>
+      </c>
+      <c r="H70" s="21">
+        <v>5</v>
+      </c>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
+      <c r="P70" s="12"/>
+      <c r="Q70" s="12"/>
+      <c r="R70" s="12"/>
+      <c r="S70" s="12"/>
+      <c r="T70" s="12"/>
+      <c r="U70" s="12"/>
+      <c r="V70" s="12"/>
+      <c r="W70" s="12"/>
+      <c r="X70" s="12"/>
+      <c r="Y70" s="12"/>
+      <c r="Z70" s="12"/>
+    </row>
+    <row r="71" ht="13.65" customHeight="1">
+      <c r="A71" t="s" s="14">
+        <v>190</v>
+      </c>
+      <c r="B71" s="34">
+        <v>70</v>
+      </c>
+      <c r="C71" t="s" s="14">
+        <v>191</v>
+      </c>
+      <c r="D71" s="16"/>
+      <c r="E71" t="s" s="14">
+        <v>192</v>
+      </c>
+      <c r="F71" s="35">
+        <v>112</v>
+      </c>
+      <c r="G71" s="21">
+        <v>45</v>
+      </c>
+      <c r="H71" s="21">
+        <v>10</v>
+      </c>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="12"/>
+      <c r="P71" s="12"/>
+      <c r="Q71" s="12"/>
+      <c r="R71" s="12"/>
+      <c r="S71" s="12"/>
+      <c r="T71" s="12"/>
+      <c r="U71" s="12"/>
+      <c r="V71" s="12"/>
+      <c r="W71" s="12"/>
+      <c r="X71" s="12"/>
+      <c r="Y71" s="12"/>
+      <c r="Z71" s="12"/>
+    </row>
+    <row r="72" ht="13.65" customHeight="1">
+      <c r="A72" s="16"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="12"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="12"/>
+      <c r="O72" s="12"/>
+      <c r="P72" s="12"/>
+      <c r="Q72" s="12"/>
+      <c r="R72" s="12"/>
+      <c r="S72" s="12"/>
+      <c r="T72" s="12"/>
+      <c r="U72" s="12"/>
+      <c r="V72" s="12"/>
+      <c r="W72" s="12"/>
+      <c r="X72" s="12"/>
+      <c r="Y72" s="12"/>
+      <c r="Z72" s="12"/>
+    </row>
+    <row r="73" ht="13.65" customHeight="1">
+      <c r="A73" s="16"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="12"/>
+      <c r="L73" s="12"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="12"/>
+      <c r="O73" s="12"/>
+      <c r="P73" s="12"/>
+      <c r="Q73" s="12"/>
+      <c r="R73" s="12"/>
+      <c r="S73" s="12"/>
+      <c r="T73" s="12"/>
+      <c r="U73" s="12"/>
+      <c r="V73" s="12"/>
+      <c r="W73" s="12"/>
+      <c r="X73" s="12"/>
+      <c r="Y73" s="12"/>
+      <c r="Z73" s="12"/>
+    </row>
+    <row r="74" ht="13.65" customHeight="1">
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="12"/>
+      <c r="P74" s="12"/>
+      <c r="Q74" s="12"/>
+      <c r="R74" s="12"/>
+      <c r="S74" s="12"/>
+      <c r="T74" s="12"/>
+      <c r="U74" s="12"/>
+      <c r="V74" s="12"/>
+      <c r="W74" s="12"/>
+      <c r="X74" s="12"/>
+      <c r="Y74" s="12"/>
+      <c r="Z74" s="12"/>
+    </row>
+    <row r="75" ht="13.65" customHeight="1">
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="12"/>
+      <c r="L75" s="12"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="12"/>
+      <c r="O75" s="12"/>
+      <c r="P75" s="12"/>
+      <c r="Q75" s="12"/>
+      <c r="R75" s="12"/>
+      <c r="S75" s="12"/>
+      <c r="T75" s="12"/>
+      <c r="U75" s="12"/>
+      <c r="V75" s="12"/>
+      <c r="W75" s="12"/>
+      <c r="X75" s="12"/>
+      <c r="Y75" s="12"/>
+      <c r="Z75" s="12"/>
+    </row>
+    <row r="76" ht="13.65" customHeight="1">
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="12"/>
+      <c r="P76" s="12"/>
+      <c r="Q76" s="12"/>
+      <c r="R76" s="12"/>
+      <c r="S76" s="12"/>
+      <c r="T76" s="12"/>
+      <c r="U76" s="12"/>
+      <c r="V76" s="12"/>
+      <c r="W76" s="12"/>
+      <c r="X76" s="12"/>
+      <c r="Y76" s="12"/>
+      <c r="Z76" s="12"/>
+    </row>
+    <row r="77" ht="13.65" customHeight="1">
+      <c r="A77" s="16"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
+      <c r="M77" s="22"/>
+      <c r="N77" s="12"/>
+      <c r="O77" s="12"/>
+      <c r="P77" s="12"/>
+      <c r="Q77" s="12"/>
+      <c r="R77" s="12"/>
+      <c r="S77" s="12"/>
+      <c r="T77" s="12"/>
+      <c r="U77" s="12"/>
+      <c r="V77" s="12"/>
+      <c r="W77" s="12"/>
+      <c r="X77" s="12"/>
+      <c r="Y77" s="12"/>
+      <c r="Z77" s="12"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C64" r:id="rId1" location="" tooltip="" display="$50 Fresh baked sweet plus $50 gift. Local bakery. Instagram Sugar &amp; Sage (@sugarnsagewi)&#10;"/>
